--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12312,7 +12312,7 @@
         <v>46269</v>
       </c>
       <c r="D519">
-        <v>228.1111111111111</v>
+        <v>228.2458333333333</v>
       </c>
       <c r="E519">
         <v>1.034610303830911</v>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12312,7 +12312,7 @@
         <v>46269</v>
       </c>
       <c r="D519">
-        <v>228.2458333333333</v>
+        <v>228.3266666666667</v>
       </c>
       <c r="E519">
         <v>1.034610303830911</v>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12312,7 +12312,7 @@
         <v>46269</v>
       </c>
       <c r="D519">
-        <v>228.3266666666667</v>
+        <v>228.7361111111111</v>
       </c>
       <c r="E519">
         <v>1.034610303830911</v>
@@ -12321,7 +12321,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G519">
-        <v>121.15</v>
+        <v>121.0633333333333</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G519"/>
+  <dimension ref="A1:G520"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12312,7 +12312,7 @@
         <v>46269</v>
       </c>
       <c r="D519">
-        <v>228.7361111111111</v>
+        <v>228.7333333333333</v>
       </c>
       <c r="E519">
         <v>1.034610303830911</v>
@@ -12321,7 +12321,30 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G519">
-        <v>121.0633333333333</v>
+        <v>120.92</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7">
+      <c r="A520">
+        <v>2026</v>
+      </c>
+      <c r="B520">
+        <v>37</v>
+      </c>
+      <c r="C520" s="1">
+        <v>46275</v>
+      </c>
+      <c r="D520">
+        <v>231.0666666666667</v>
+      </c>
+      <c r="E520">
+        <v>1.034610303830911</v>
+      </c>
+      <c r="F520">
+        <v>125.6223830911493</v>
+      </c>
+      <c r="G520">
+        <v>120.49</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12335,7 +12335,7 @@
         <v>46275</v>
       </c>
       <c r="D520">
-        <v>231.0666666666667</v>
+        <v>231.05</v>
       </c>
       <c r="E520">
         <v>1.034610303830911</v>
@@ -12344,7 +12344,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G520">
-        <v>120.49</v>
+        <v>120.52</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12344,7 +12344,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G520">
-        <v>120.52</v>
+        <v>120.46</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12344,7 +12344,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G520">
-        <v>120.46</v>
+        <v>120.4525</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12335,7 +12335,7 @@
         <v>46275</v>
       </c>
       <c r="D520">
-        <v>231.05</v>
+        <v>231.5366666666667</v>
       </c>
       <c r="E520">
         <v>1.034610303830911</v>
@@ -12344,7 +12344,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G520">
-        <v>120.4525</v>
+        <v>120.448</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12335,7 +12335,7 @@
         <v>46275</v>
       </c>
       <c r="D520">
-        <v>231.5366666666667</v>
+        <v>231.9444444444445</v>
       </c>
       <c r="E520">
         <v>1.034610303830911</v>
@@ -12344,7 +12344,7 @@
         <v>125.6223830911493</v>
       </c>
       <c r="G520">
-        <v>120.448</v>
+        <v>120.645</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12335,16 +12335,16 @@
         <v>46275</v>
       </c>
       <c r="D520">
-        <v>231.9444444444445</v>
+        <v>232.71</v>
       </c>
       <c r="E520">
-        <v>1.034610303830911</v>
+        <v>1.074557463672391</v>
       </c>
       <c r="F520">
-        <v>125.6223830911493</v>
+        <v>130.2150890356671</v>
       </c>
       <c r="G520">
-        <v>120.645</v>
+        <v>120.928</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G520"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12344,7 +12344,30 @@
         <v>130.2150890356671</v>
       </c>
       <c r="G520">
-        <v>120.928</v>
+        <v>120.898</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7">
+      <c r="A521">
+        <v>2026</v>
+      </c>
+      <c r="B521">
+        <v>38</v>
+      </c>
+      <c r="C521" s="1">
+        <v>46282</v>
+      </c>
+      <c r="D521">
+        <v>237.8</v>
+      </c>
+      <c r="E521">
+        <v>1.101188903566711</v>
+      </c>
+      <c r="F521">
+        <v>133.276892998679</v>
+      </c>
+      <c r="G521">
+        <v>121.18</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,7 +12358,7 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>237.8</v>
+        <v>239.3833333333333</v>
       </c>
       <c r="E521">
         <v>1.101188903566711</v>
@@ -12367,7 +12367,7 @@
         <v>133.276892998679</v>
       </c>
       <c r="G521">
-        <v>121.18</v>
+        <v>121.77</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,7 +12358,7 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>239.3833333333333</v>
+        <v>239.9111111111111</v>
       </c>
       <c r="E521">
         <v>1.101188903566711</v>
@@ -12367,7 +12367,7 @@
         <v>133.276892998679</v>
       </c>
       <c r="G521">
-        <v>121.77</v>
+        <v>121.6833333333333</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,7 +12358,7 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>239.9111111111111</v>
+        <v>240.175</v>
       </c>
       <c r="E521">
         <v>1.101188903566711</v>
@@ -12367,7 +12367,7 @@
         <v>133.276892998679</v>
       </c>
       <c r="G521">
-        <v>121.6833333333333</v>
+        <v>121.6725</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,7 +12358,7 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>240.175</v>
+        <v>241.6</v>
       </c>
       <c r="E521">
         <v>1.101188903566711</v>
@@ -12367,7 +12367,7 @@
         <v>133.276892998679</v>
       </c>
       <c r="G521">
-        <v>121.6725</v>
+        <v>121.666</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,7 +12358,7 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>241.6</v>
+        <v>242.4388888888889</v>
       </c>
       <c r="E521">
         <v>1.101188903566711</v>
@@ -12367,7 +12367,7 @@
         <v>133.276892998679</v>
       </c>
       <c r="G521">
-        <v>121.666</v>
+        <v>121.3816666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,16 +12358,16 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>242.4388888888889</v>
+        <v>243.3833333333333</v>
       </c>
       <c r="E521">
-        <v>1.101188903566711</v>
+        <v>1.123513870541612</v>
       </c>
       <c r="F521">
-        <v>133.276892998679</v>
+        <v>135.8471122853368</v>
       </c>
       <c r="G521">
-        <v>121.3816666666667</v>
+        <v>121.2216666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12367,7 +12367,30 @@
         <v>135.8471122853368</v>
       </c>
       <c r="G521">
-        <v>121.2216666666667</v>
+        <v>121.255</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7">
+      <c r="A522">
+        <v>2026</v>
+      </c>
+      <c r="B522">
+        <v>39</v>
+      </c>
+      <c r="C522" s="1">
+        <v>46289</v>
+      </c>
+      <c r="D522">
+        <v>247.1333333333333</v>
+      </c>
+      <c r="E522">
+        <v>1.145838837516512</v>
+      </c>
+      <c r="F522">
+        <v>138.4173315719947</v>
+      </c>
+      <c r="G522">
+        <v>120.94</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12381,7 +12381,7 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>247.1333333333333</v>
+        <v>248.9666666666667</v>
       </c>
       <c r="E522">
         <v>1.145838837516512</v>
@@ -12390,7 +12390,7 @@
         <v>138.4173315719947</v>
       </c>
       <c r="G522">
-        <v>120.94</v>
+        <v>121.4</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12381,7 +12381,7 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>248.9666666666667</v>
+        <v>249.5777777777778</v>
       </c>
       <c r="E522">
         <v>1.145838837516512</v>
@@ -12390,7 +12390,7 @@
         <v>138.4173315719947</v>
       </c>
       <c r="G522">
-        <v>121.4</v>
+        <v>120.3266666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12358,16 +12358,16 @@
         <v>46282</v>
       </c>
       <c r="D521">
-        <v>243.3833333333333</v>
+        <v>242.7333333333333</v>
       </c>
       <c r="E521">
-        <v>1.123513870541612</v>
+        <v>1.119048877146631</v>
       </c>
       <c r="F521">
-        <v>135.8471122853368</v>
+        <v>135.3330684280053</v>
       </c>
       <c r="G521">
-        <v>121.255</v>
+        <v>121.318</v>
       </c>
     </row>
     <row r="522" spans="1:7">
@@ -12381,7 +12381,7 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>249.5777777777778</v>
+        <v>250.4666666666667</v>
       </c>
       <c r="E522">
         <v>1.145838837516512</v>
@@ -12390,7 +12390,7 @@
         <v>138.4173315719947</v>
       </c>
       <c r="G522">
-        <v>120.3266666666667</v>
+        <v>120.1925</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12381,7 +12381,7 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>250.4666666666667</v>
+        <v>250.7666666666667</v>
       </c>
       <c r="E522">
         <v>1.145838837516512</v>
@@ -12390,7 +12390,7 @@
         <v>138.4173315719947</v>
       </c>
       <c r="G522">
-        <v>120.1925</v>
+        <v>120.236</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12381,16 +12381,16 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>250.7666666666667</v>
+        <v>251.0777777777778</v>
       </c>
       <c r="E522">
-        <v>1.145838837516512</v>
+        <v>1.143372963452224</v>
       </c>
       <c r="F522">
-        <v>138.4173315719947</v>
+        <v>137.9714566270365</v>
       </c>
       <c r="G522">
-        <v>120.236</v>
+        <v>120.265</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12381,16 +12381,16 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>251.0777777777778</v>
+        <v>251.347619047619</v>
       </c>
       <c r="E522">
-        <v>1.143372963452224</v>
+        <v>1.142668428005284</v>
       </c>
       <c r="F522">
-        <v>137.9714566270365</v>
+        <v>137.8440637856199</v>
       </c>
       <c r="G522">
-        <v>120.265</v>
+        <v>120.3057142857143</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G522"/>
+  <dimension ref="A1:G523"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12381,16 +12381,39 @@
         <v>46289</v>
       </c>
       <c r="D522">
-        <v>251.347619047619</v>
+        <v>251.2444444444444</v>
       </c>
       <c r="E522">
-        <v>1.142668428005284</v>
+        <v>1.142140026420079</v>
       </c>
       <c r="F522">
-        <v>137.8440637856199</v>
+        <v>137.7485191545575</v>
       </c>
       <c r="G522">
-        <v>120.3057142857143</v>
+        <v>120.42</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7">
+      <c r="A523">
+        <v>2026</v>
+      </c>
+      <c r="B523">
+        <v>40</v>
+      </c>
+      <c r="C523" s="1">
+        <v>46296</v>
+      </c>
+      <c r="D523">
+        <v>252.9666666666667</v>
+      </c>
+      <c r="E523">
+        <v>1.138441215323646</v>
+      </c>
+      <c r="F523">
+        <v>137.0797067371202</v>
+      </c>
+      <c r="G523">
+        <v>120.65</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,7 +12404,7 @@
         <v>46296</v>
       </c>
       <c r="D523">
-        <v>252.9666666666667</v>
+        <v>253.375</v>
       </c>
       <c r="E523">
         <v>1.138441215323646</v>
@@ -12413,7 +12413,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G523">
-        <v>120.65</v>
+        <v>121.26</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,7 +12404,7 @@
         <v>46296</v>
       </c>
       <c r="D523">
-        <v>253.375</v>
+        <v>253.5111111111111</v>
       </c>
       <c r="E523">
         <v>1.138441215323646</v>
@@ -12413,7 +12413,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G523">
-        <v>121.26</v>
+        <v>121.9066666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,7 +12404,7 @@
         <v>46296</v>
       </c>
       <c r="D523">
-        <v>253.5111111111111</v>
+        <v>253.5791666666667</v>
       </c>
       <c r="E523">
         <v>1.138441215323646</v>
@@ -12413,7 +12413,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G523">
-        <v>121.9066666666667</v>
+        <v>121.9875</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12401,10 +12401,10 @@
         <v>40</v>
       </c>
       <c r="C523" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D523">
-        <v>253.5791666666667</v>
+        <v>254.675</v>
       </c>
       <c r="E523">
         <v>1.138441215323646</v>
@@ -12413,7 +12413,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G523">
-        <v>121.9875</v>
+        <v>122.2425</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,16 +12404,16 @@
         <v>46297</v>
       </c>
       <c r="D523">
-        <v>254.675</v>
+        <v>254.8533333333333</v>
       </c>
       <c r="E523">
-        <v>1.138441215323646</v>
+        <v>1.122377807133421</v>
       </c>
       <c r="F523">
-        <v>137.0797067371202</v>
+        <v>135.9670272126816</v>
       </c>
       <c r="G523">
-        <v>122.2425</v>
+        <v>122.25</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,16 +12404,16 @@
         <v>46297</v>
       </c>
       <c r="D523">
-        <v>254.8533333333333</v>
+        <v>255.21</v>
       </c>
       <c r="E523">
-        <v>1.122377807133421</v>
+        <v>1.114346103038309</v>
       </c>
       <c r="F523">
-        <v>135.9670272126816</v>
+        <v>135.4106874504623</v>
       </c>
       <c r="G523">
-        <v>122.25</v>
+        <v>122.048</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G523"/>
+  <dimension ref="A1:G524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12413,7 +12413,30 @@
         <v>135.4106874504623</v>
       </c>
       <c r="G523">
-        <v>122.048</v>
+        <v>122.248</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7">
+      <c r="A524">
+        <v>2026</v>
+      </c>
+      <c r="B524">
+        <v>41</v>
+      </c>
+      <c r="C524" s="1">
+        <v>46303</v>
+      </c>
+      <c r="D524">
+        <v>255.5666666666667</v>
+      </c>
+      <c r="E524">
+        <v>1.098282694848085</v>
+      </c>
+      <c r="F524">
+        <v>134.2980079260238</v>
+      </c>
+      <c r="G524">
+        <v>122.75</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12404,16 +12404,16 @@
         <v>46297</v>
       </c>
       <c r="D523">
-        <v>255.21</v>
+        <v>254.9722222222222</v>
       </c>
       <c r="E523">
-        <v>1.114346103038309</v>
+        <v>1.138441215323646</v>
       </c>
       <c r="F523">
-        <v>135.4106874504623</v>
+        <v>137.0797067371202</v>
       </c>
       <c r="G523">
-        <v>122.248</v>
+        <v>122.4033333333333</v>
       </c>
     </row>
     <row r="524" spans="1:7">
@@ -12430,13 +12430,13 @@
         <v>255.5666666666667</v>
       </c>
       <c r="E524">
-        <v>1.098282694848085</v>
+        <v>1.138441215323646</v>
       </c>
       <c r="F524">
-        <v>134.2980079260238</v>
+        <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>122.75</v>
+        <v>122.47</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12427,7 +12427,7 @@
         <v>46303</v>
       </c>
       <c r="D524">
-        <v>255.5666666666667</v>
+        <v>255.4555555555555</v>
       </c>
       <c r="E524">
         <v>1.138441215323646</v>
@@ -12436,7 +12436,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>122.47</v>
+        <v>122.21</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12427,7 +12427,7 @@
         <v>46303</v>
       </c>
       <c r="D524">
-        <v>255.4555555555555</v>
+        <v>255.4</v>
       </c>
       <c r="E524">
         <v>1.138441215323646</v>
@@ -12436,7 +12436,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>122.21</v>
+        <v>122.1775</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12424,10 +12424,10 @@
         <v>41</v>
       </c>
       <c r="C524" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D524">
-        <v>255.4</v>
+        <v>255.3166666666667</v>
       </c>
       <c r="E524">
         <v>1.138441215323646</v>
@@ -12436,7 +12436,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>122.1775</v>
+        <v>122.0575</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12427,7 +12427,7 @@
         <v>46304</v>
       </c>
       <c r="D524">
-        <v>255.3166666666667</v>
+        <v>255.3</v>
       </c>
       <c r="E524">
         <v>1.138441215323646</v>
@@ -12436,7 +12436,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>122.0575</v>
+        <v>121.994</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12427,7 +12427,7 @@
         <v>46304</v>
       </c>
       <c r="D524">
-        <v>255.3</v>
+        <v>255.2888888888889</v>
       </c>
       <c r="E524">
         <v>1.138441215323646</v>
@@ -12436,7 +12436,7 @@
         <v>137.0797067371202</v>
       </c>
       <c r="G524">
-        <v>121.994</v>
+        <v>121.9516666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G524"/>
+  <dimension ref="A1:G525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12427,16 +12427,39 @@
         <v>46304</v>
       </c>
       <c r="D524">
-        <v>255.2888888888889</v>
+        <v>255.3</v>
       </c>
       <c r="E524">
-        <v>1.138441215323646</v>
+        <v>1.113236459709379</v>
       </c>
       <c r="F524">
-        <v>137.0797067371202</v>
+        <v>135.0842208718626</v>
       </c>
       <c r="G524">
-        <v>121.9516666666667</v>
+        <v>121.946</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7">
+      <c r="A525">
+        <v>2026</v>
+      </c>
+      <c r="B525">
+        <v>42</v>
+      </c>
+      <c r="C525" s="1">
+        <v>46310</v>
+      </c>
+      <c r="D525">
+        <v>255.2333333333333</v>
+      </c>
+      <c r="E525">
+        <v>1.096433289299868</v>
+      </c>
+      <c r="F525">
+        <v>133.7538969616909</v>
+      </c>
+      <c r="G525">
+        <v>121.84</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12459,7 +12459,7 @@
         <v>133.7538969616909</v>
       </c>
       <c r="G525">
-        <v>121.84</v>
+        <v>121.7</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12459,7 +12459,7 @@
         <v>133.7538969616909</v>
       </c>
       <c r="G525">
-        <v>121.7</v>
+        <v>121.2533333333333</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12427,16 +12427,16 @@
         <v>46304</v>
       </c>
       <c r="D524">
-        <v>255.3</v>
+        <v>255.3166666666667</v>
       </c>
       <c r="E524">
-        <v>1.113236459709379</v>
+        <v>1.117437252311757</v>
       </c>
       <c r="F524">
-        <v>135.0842208718626</v>
+        <v>135.4168018494055</v>
       </c>
       <c r="G524">
-        <v>121.946</v>
+        <v>121.9725</v>
       </c>
     </row>
     <row r="525" spans="1:7">
@@ -12459,7 +12459,7 @@
         <v>133.7538969616909</v>
       </c>
       <c r="G525">
-        <v>121.2533333333333</v>
+        <v>121.1975</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12450,7 +12450,7 @@
         <v>46310</v>
       </c>
       <c r="D525">
-        <v>255.2333333333333</v>
+        <v>255.3666666666666</v>
       </c>
       <c r="E525">
         <v>1.096433289299868</v>
@@ -12459,7 +12459,7 @@
         <v>133.7538969616909</v>
       </c>
       <c r="G525">
-        <v>121.1975</v>
+        <v>121.164</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12450,7 +12450,7 @@
         <v>46310</v>
       </c>
       <c r="D525">
-        <v>255.3666666666666</v>
+        <v>255.4555555555555</v>
       </c>
       <c r="E525">
         <v>1.096433289299868</v>
@@ -12459,7 +12459,7 @@
         <v>133.7538969616909</v>
       </c>
       <c r="G525">
-        <v>121.164</v>
+        <v>121.3016666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12450,16 +12450,16 @@
         <v>46310</v>
       </c>
       <c r="D525">
-        <v>255.4555555555555</v>
+        <v>255.9033333333333</v>
       </c>
       <c r="E525">
-        <v>1.096433289299868</v>
+        <v>1.091836195508587</v>
       </c>
       <c r="F525">
-        <v>133.7538969616909</v>
+        <v>132.8795313077939</v>
       </c>
       <c r="G525">
-        <v>121.3016666666667</v>
+        <v>121.424</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G525"/>
+  <dimension ref="A1:G526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12459,7 +12459,30 @@
         <v>132.8795313077939</v>
       </c>
       <c r="G525">
-        <v>121.424</v>
+        <v>121.384</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7">
+      <c r="A526">
+        <v>2026</v>
+      </c>
+      <c r="B526">
+        <v>43</v>
+      </c>
+      <c r="C526" s="1">
+        <v>46317</v>
+      </c>
+      <c r="D526">
+        <v>256.6666666666667</v>
+      </c>
+      <c r="E526">
+        <v>1.088771466314399</v>
+      </c>
+      <c r="F526">
+        <v>132.2966208718626</v>
+      </c>
+      <c r="G526">
+        <v>121.24</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12482,7 +12482,7 @@
         <v>132.2966208718626</v>
       </c>
       <c r="G526">
-        <v>121.24</v>
+        <v>121.55</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12482,7 +12482,7 @@
         <v>132.2966208718626</v>
       </c>
       <c r="G526">
-        <v>121.55</v>
+        <v>121.6366666666667</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12482,7 +12482,7 @@
         <v>132.2966208718626</v>
       </c>
       <c r="G526">
-        <v>121.6366666666667</v>
+        <v>121.6475</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12473,7 +12473,7 @@
         <v>46317</v>
       </c>
       <c r="D526">
-        <v>256.6666666666667</v>
+        <v>256.78</v>
       </c>
       <c r="E526">
         <v>1.088771466314399</v>
@@ -12482,7 +12482,7 @@
         <v>132.2966208718626</v>
       </c>
       <c r="G526">
-        <v>121.6475</v>
+        <v>121.654</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12473,16 +12473,16 @@
         <v>46317</v>
       </c>
       <c r="D526">
-        <v>256.78</v>
+        <v>256.8555555555556</v>
       </c>
       <c r="E526">
         <v>1.088771466314399</v>
       </c>
       <c r="F526">
-        <v>132.2966208718626</v>
+        <v>132.4454196389256</v>
       </c>
       <c r="G526">
-        <v>121.654</v>
+        <v>121.7383333333333</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12473,16 +12473,16 @@
         <v>46317</v>
       </c>
       <c r="D526">
-        <v>256.8555555555556</v>
+        <v>257.0066666666667</v>
       </c>
       <c r="E526">
         <v>1.088771466314399</v>
       </c>
       <c r="F526">
-        <v>132.4454196389256</v>
+        <v>132.564458652576</v>
       </c>
       <c r="G526">
-        <v>121.7383333333333</v>
+        <v>121.962</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G526"/>
+  <dimension ref="A1:G527"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="1" customWidth="1"/>
@@ -12482,7 +12482,30 @@
         <v>132.564458652576</v>
       </c>
       <c r="G526">
-        <v>121.962</v>
+        <v>121.892</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7">
+      <c r="A527">
+        <v>2026</v>
+      </c>
+      <c r="B527">
+        <v>44</v>
+      </c>
+      <c r="C527" s="1">
+        <v>46324</v>
+      </c>
+      <c r="D527">
+        <v>257.2333333333333</v>
+      </c>
+      <c r="E527">
+        <v>1.088771466314399</v>
+      </c>
+      <c r="F527">
+        <v>132.7430171730515</v>
+      </c>
+      <c r="G527">
+        <v>121.98</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12505,7 +12505,7 @@
         <v>132.7430171730515</v>
       </c>
       <c r="G527">
-        <v>121.98</v>
+        <v>122.01</v>
       </c>
     </row>
   </sheetData>

--- a/vikur_fra_2017.xlsx
+++ b/vikur_fra_2017.xlsx
@@ -12473,16 +12473,16 @@
         <v>46317</v>
       </c>
       <c r="D526">
-        <v>257.0066666666667</v>
+        <v>256.95</v>
       </c>
       <c r="E526">
         <v>1.088771466314399</v>
       </c>
       <c r="F526">
-        <v>132.564458652576</v>
+        <v>132.5198190224571</v>
       </c>
       <c r="G526">
-        <v>121.892</v>
+        <v>121.7825</v>
       </c>
     </row>
     <row r="527" spans="1:7">
@@ -12505,7 +12505,7 @@
         <v>132.7430171730515</v>
       </c>
       <c r="G527">
-        <v>122.01</v>
+        <v>121.8233333333333</v>
       </c>
     </row>
   </sheetData>
